--- a/SGC-CKN/Excel/71606ae7-fad8-4192-8123-01ee5a8e13f4_Lô_CT-02_P1_53_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/71606ae7-fad8-4192-8123-01ee5a8e13f4_Lô_CT-02_P1_53_D800_31-03-2026.xlsx
@@ -161,7 +161,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">18:52
+    <t xml:space="preserve">18:32
 31/03/2026</t>
   </si>
   <si>
@@ -1265,16 +1265,16 @@
         <v>-5.7</v>
       </c>
       <c r="G14" s="16">
-        <v>-7.9</v>
+        <v>-9</v>
       </c>
       <c r="H14" s="16">
         <v>1.08</v>
       </c>
       <c r="I14" s="16">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J14" s="8">
-        <v>2.03</v>
+        <v>3.05</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>41</v>
@@ -1297,19 +1297,19 @@
         <v>44</v>
       </c>
       <c r="F15" s="19">
-        <v>-7.9</v>
+        <v>-9</v>
       </c>
       <c r="G15" s="19">
-        <v>-12.8</v>
+        <v>-17.8</v>
       </c>
       <c r="H15" s="19">
         <v>1</v>
       </c>
       <c r="I15" s="19">
-        <v>4.9</v>
-      </c>
-      <c r="J15" s="8">
-        <v>4.9</v>
+        <v>8.8</v>
+      </c>
+      <c r="J15" s="15">
+        <v>8.8</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1332,19 +1332,19 @@
         <v>47</v>
       </c>
       <c r="F16" s="22">
-        <v>-12.8</v>
+        <v>-17.8</v>
       </c>
       <c r="G16" s="22">
         <v>-22</v>
       </c>
       <c r="H16" s="22">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="I16" s="22">
-        <v>9.2</v>
-      </c>
-      <c r="J16" s="15">
-        <v>6.73</v>
+        <v>4.2</v>
+      </c>
+      <c r="J16" s="8">
+        <v>4.06</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>48</v>
@@ -1373,13 +1373,13 @@
         <v>-35.56</v>
       </c>
       <c r="H17" s="25">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="I17" s="25">
         <v>13.56</v>
       </c>
       <c r="J17" s="15">
-        <v>6.12</v>
+        <v>5.32</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1659,16 +1659,16 @@
         <v>-5.7</v>
       </c>
       <c r="F5" s="16">
-        <v>-7.9</v>
+        <v>-9</v>
       </c>
       <c r="G5" s="16">
         <v>1.08</v>
       </c>
       <c r="H5" s="16">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="I5" s="8">
-        <v>2.03</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1685,19 +1685,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-7.9</v>
+        <v>-9</v>
       </c>
       <c r="F6" s="19">
-        <v>-12.8</v>
+        <v>-17.8</v>
       </c>
       <c r="G6" s="19">
         <v>1</v>
       </c>
       <c r="H6" s="19">
-        <v>4.9</v>
-      </c>
-      <c r="I6" s="8">
-        <v>4.9</v>
+        <v>8.8</v>
+      </c>
+      <c r="I6" s="15">
+        <v>8.8</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1714,19 +1714,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-12.8</v>
+        <v>-17.8</v>
       </c>
       <c r="F7" s="22">
         <v>-22</v>
       </c>
       <c r="G7" s="22">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="H7" s="22">
-        <v>9.2</v>
-      </c>
-      <c r="I7" s="15">
-        <v>6.73</v>
+        <v>4.2</v>
+      </c>
+      <c r="I7" s="8">
+        <v>4.06</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1749,13 +1749,13 @@
         <v>-35.56</v>
       </c>
       <c r="G8" s="25">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="H8" s="25">
         <v>13.56</v>
       </c>
       <c r="I8" s="15">
-        <v>6.12</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
